--- a/CTEHE2019/Proyectos/EjemploI_2526_Option3/Documentacion/EjemploI_Option3_Comparacion_Resultados.xlsx
+++ b/CTEHE2019/Proyectos/EjemploI_2526_Option3/Documentacion/EjemploI_Option3_Comparacion_Resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProyectosCTEyCEE\CTEHE2019\Proyectos\EjemploI_2526_Option3\Documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5442E3E9-0A31-4A94-8AB1-A1C86C1F85FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E509306-FD98-481C-B94B-11A797249DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="48" yWindow="12264" windowWidth="24888" windowHeight="12960" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14784" yWindow="4896" windowWidth="24888" windowHeight="12960" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Geometria" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="Solar" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -123,61 +124,61 @@
     <t>180.60           20.11</t>
   </si>
   <si>
-    <t>ESQUINA_CONCAVA_CERRAMIENTO*18.000000</t>
-  </si>
-  <si>
-    <t>ESQUINA_CONVEXA_CERRAMIENTO*0.000000</t>
-  </si>
-  <si>
-    <t>UNION_CUBIERTA*55.712814</t>
-  </si>
-  <si>
-    <t>ESQUINA_CONVEXA_FORJADO*0.000000</t>
-  </si>
-  <si>
-    <t>FRENTE_FORJADO*47.000000</t>
-  </si>
-  <si>
-    <t>UNION_T_CERRAMIENTO*0.000000</t>
-  </si>
-  <si>
-    <t>PILAR*0.000000</t>
-  </si>
-  <si>
-    <t>HUECO_VENTANA*54.600002</t>
-  </si>
-  <si>
-    <t>ESQUINA_CONCAVA_TERRENO*36.000000</t>
-  </si>
-  <si>
-    <t>ESQUINA_CONVEXA_TERRENO*0.000000</t>
-  </si>
-  <si>
-    <t>CONTINUO_TERRENO*0.000000</t>
-  </si>
-  <si>
-    <t>UNION_VERTICAL_ENT_EXT*0.000000</t>
-  </si>
-  <si>
-    <t>UNION_SOLERA_PAREDEXT*0.000000</t>
-  </si>
-  <si>
-    <t>MURO-EXT-AISLADO*0.000000</t>
-  </si>
-  <si>
-    <t>OTROS*23.200001</t>
-  </si>
-  <si>
-    <t>HUECO_DINTEL*0.000000</t>
-  </si>
-  <si>
-    <t>HUECO_CAPIALZADO*21.000000</t>
-  </si>
-  <si>
-    <t>HUECO_JAMBA*42.000000</t>
-  </si>
-  <si>
-    <t>HUECO_ALFEIZAR*21.000000</t>
+    <t>ESQUINA_CONCAVA_CERRAMIENTO</t>
+  </si>
+  <si>
+    <t>ESQUINA_CONVEXA_CERRAMIENTO</t>
+  </si>
+  <si>
+    <t>UNION_CUBIERTA</t>
+  </si>
+  <si>
+    <t>ESQUINA_CONVEXA_FORJADO</t>
+  </si>
+  <si>
+    <t>FRENTE_FORJADO</t>
+  </si>
+  <si>
+    <t>UNION_T_CERRAMIENTO</t>
+  </si>
+  <si>
+    <t>PILAR</t>
+  </si>
+  <si>
+    <t>HUECO_VENTANA</t>
+  </si>
+  <si>
+    <t>ESQUINA_CONCAVA_TERRENO</t>
+  </si>
+  <si>
+    <t>ESQUINA_CONVEXA_TERRENO</t>
+  </si>
+  <si>
+    <t>CONTINUO_TERRENO</t>
+  </si>
+  <si>
+    <t>UNION_VERTICAL_ENT_EXT</t>
+  </si>
+  <si>
+    <t>UNION_SOLERA_PAREDEXT</t>
+  </si>
+  <si>
+    <t>MURO-EXT-AISLADO</t>
+  </si>
+  <si>
+    <t>OTROS</t>
+  </si>
+  <si>
+    <t>HUECO_DINTEL</t>
+  </si>
+  <si>
+    <t>HUECO_CAPIALZADO</t>
+  </si>
+  <si>
+    <t>HUECO_JAMBA</t>
+  </si>
+  <si>
+    <t>HUECO_ALFEIZAR</t>
   </si>
 </sst>
 </file>
@@ -389,62 +390,62 @@
   </cellStyleXfs>
   <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1241,251 +1242,251 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="66" spans="11:15">
-      <c r="K66" s="1" t="s">
+      <c r="K66" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="L66" s="1"/>
-      <c r="M66" s="1"/>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
+      <c r="L66" s="16"/>
+      <c r="M66" s="16"/>
+      <c r="N66" s="16"/>
+      <c r="O66" s="16"/>
     </row>
     <row r="67" spans="11:15" ht="28.8">
-      <c r="K67" s="2" t="s">
+      <c r="K67" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="L67" s="2"/>
-      <c r="M67" s="3" t="s">
+      <c r="L67" s="17"/>
+      <c r="M67" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N67" s="4" t="s">
+      <c r="N67" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="O67" s="5" t="s">
+      <c r="O67" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="68" spans="11:15">
-      <c r="K68" s="6"/>
-      <c r="L68" s="6"/>
-      <c r="M68" s="6"/>
-      <c r="N68" s="6"/>
-      <c r="O68" s="6"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
     </row>
     <row r="69" spans="11:15">
-      <c r="K69" s="7" t="s">
+      <c r="K69" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="L69" s="8"/>
-      <c r="M69" s="9">
+      <c r="L69" s="15"/>
+      <c r="M69" s="5">
         <v>0.1</v>
       </c>
-      <c r="N69" s="9">
+      <c r="N69" s="5">
         <v>32</v>
       </c>
-      <c r="O69" s="9">
+      <c r="O69" s="5">
         <v>3.2</v>
       </c>
     </row>
     <row r="70" spans="11:15">
-      <c r="K70" s="6"/>
-      <c r="L70" s="6"/>
-      <c r="M70" s="6"/>
-      <c r="N70" s="6"/>
-      <c r="O70" s="6"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
     </row>
     <row r="71" spans="11:15">
-      <c r="K71" s="7" t="s">
+      <c r="K71" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="L71" s="8"/>
-      <c r="M71" s="9">
+      <c r="L71" s="15"/>
+      <c r="M71" s="5">
         <v>0.22500000000000001</v>
       </c>
-      <c r="N71" s="9">
+      <c r="N71" s="5">
         <v>32</v>
       </c>
-      <c r="O71" s="9">
+      <c r="O71" s="5">
         <v>7.2</v>
       </c>
     </row>
     <row r="72" spans="11:15">
-      <c r="K72" s="11"/>
-      <c r="L72" s="11"/>
-      <c r="M72" s="11"/>
-      <c r="N72" s="10"/>
-      <c r="O72" s="9">
+      <c r="K72" s="18"/>
+      <c r="L72" s="18"/>
+      <c r="M72" s="18"/>
+      <c r="N72" s="19"/>
+      <c r="O72" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="11:15">
-      <c r="K73" s="6"/>
-      <c r="L73" s="6"/>
-      <c r="M73" s="6"/>
-      <c r="N73" s="6"/>
-      <c r="O73" s="6"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="4"/>
+      <c r="M73" s="4"/>
+      <c r="N73" s="4"/>
+      <c r="O73" s="4"/>
     </row>
     <row r="74" spans="11:15">
-      <c r="K74" s="7" t="s">
+      <c r="K74" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L74" s="8"/>
-      <c r="M74" s="9">
+      <c r="L74" s="15"/>
+      <c r="M74" s="5">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="N74" s="9">
+      <c r="N74" s="5">
         <v>40.6</v>
       </c>
-      <c r="O74" s="9">
+      <c r="O74" s="5">
         <v>1.75</v>
       </c>
     </row>
     <row r="75" spans="11:15">
-      <c r="K75" s="6"/>
-      <c r="L75" s="6"/>
-      <c r="M75" s="6"/>
-      <c r="N75" s="6"/>
-      <c r="O75" s="6"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="4"/>
+      <c r="N75" s="4"/>
+      <c r="O75" s="4"/>
     </row>
     <row r="76" spans="11:15">
-      <c r="K76" s="12" t="s">
+      <c r="K76" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="L76" s="13"/>
-      <c r="M76" s="14"/>
-      <c r="N76" s="14"/>
-      <c r="O76" s="15">
+      <c r="L76" s="11"/>
+      <c r="M76" s="6"/>
+      <c r="N76" s="6"/>
+      <c r="O76" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="11:15">
-      <c r="K77" s="6"/>
-      <c r="L77" s="6"/>
-      <c r="M77" s="6"/>
-      <c r="N77" s="6"/>
-      <c r="O77" s="6"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
     </row>
     <row r="78" spans="11:15">
-      <c r="K78" s="12" t="s">
+      <c r="K78" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L78" s="13"/>
-      <c r="M78" s="14"/>
-      <c r="N78" s="14"/>
-      <c r="O78" s="15">
+      <c r="L78" s="11"/>
+      <c r="M78" s="6"/>
+      <c r="N78" s="6"/>
+      <c r="O78" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="11:15">
-      <c r="K79" s="6"/>
-      <c r="L79" s="6"/>
-      <c r="M79" s="6"/>
-      <c r="N79" s="6"/>
-      <c r="O79" s="6"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4"/>
+      <c r="N79" s="4"/>
+      <c r="O79" s="4"/>
     </row>
     <row r="80" spans="11:15">
-      <c r="K80" s="7" t="s">
+      <c r="K80" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="L80" s="8"/>
-      <c r="M80" s="9">
+      <c r="L80" s="15"/>
+      <c r="M80" s="5">
         <v>0.51</v>
       </c>
-      <c r="N80" s="9">
+      <c r="N80" s="5">
         <v>13</v>
       </c>
-      <c r="O80" s="9">
+      <c r="O80" s="5">
         <v>6.63</v>
       </c>
     </row>
     <row r="81" spans="11:19">
-      <c r="K81" s="16"/>
-      <c r="L81" s="16"/>
-      <c r="M81" s="9">
+      <c r="K81" s="8"/>
+      <c r="L81" s="8"/>
+      <c r="M81" s="5">
         <v>0.08</v>
       </c>
-      <c r="N81" s="9">
+      <c r="N81" s="5">
         <v>4</v>
       </c>
-      <c r="O81" s="9">
+      <c r="O81" s="5">
         <v>0.32</v>
       </c>
     </row>
     <row r="82" spans="11:19">
-      <c r="K82" s="6"/>
-      <c r="L82" s="6"/>
-      <c r="M82" s="6"/>
-      <c r="N82" s="6"/>
-      <c r="O82" s="6"/>
+      <c r="K82" s="4"/>
+      <c r="L82" s="4"/>
+      <c r="M82" s="4"/>
+      <c r="N82" s="4"/>
+      <c r="O82" s="4"/>
     </row>
     <row r="83" spans="11:19">
-      <c r="K83" s="7" t="s">
+      <c r="K83" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="L83" s="8"/>
-      <c r="M83" s="9">
+      <c r="L83" s="15"/>
+      <c r="M83" s="5">
         <v>0.01</v>
       </c>
-      <c r="N83" s="9">
+      <c r="N83" s="5">
         <v>13</v>
       </c>
-      <c r="O83" s="9">
+      <c r="O83" s="5">
         <v>0.13</v>
       </c>
     </row>
     <row r="84" spans="11:19">
-      <c r="K84" s="16"/>
-      <c r="L84" s="16"/>
-      <c r="M84" s="9">
+      <c r="K84" s="8"/>
+      <c r="L84" s="8"/>
+      <c r="M84" s="5">
         <v>0.01</v>
       </c>
-      <c r="N84" s="9">
+      <c r="N84" s="5">
         <v>4</v>
       </c>
-      <c r="O84" s="9">
+      <c r="O84" s="5">
         <v>0.04</v>
       </c>
     </row>
     <row r="85" spans="11:19">
-      <c r="K85" s="6"/>
-      <c r="L85" s="6"/>
-      <c r="M85" s="6"/>
-      <c r="N85" s="6"/>
-      <c r="O85" s="6"/>
+      <c r="K85" s="4"/>
+      <c r="L85" s="4"/>
+      <c r="M85" s="4"/>
+      <c r="N85" s="4"/>
+      <c r="O85" s="4"/>
     </row>
     <row r="86" spans="11:19">
-      <c r="K86" s="7" t="s">
+      <c r="K86" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="L86" s="8"/>
-      <c r="M86" s="9">
+      <c r="L86" s="15"/>
+      <c r="M86" s="5">
         <v>0.02</v>
       </c>
-      <c r="N86" s="9">
+      <c r="N86" s="5">
         <v>22</v>
       </c>
-      <c r="O86" s="9">
+      <c r="O86" s="5">
         <v>0.44</v>
       </c>
     </row>
     <row r="87" spans="11:19">
-      <c r="K87" s="16"/>
-      <c r="L87" s="16"/>
-      <c r="M87" s="9">
+      <c r="K87" s="8"/>
+      <c r="L87" s="8"/>
+      <c r="M87" s="5">
         <v>0.02</v>
       </c>
-      <c r="N87" s="9">
+      <c r="N87" s="5">
         <v>20</v>
       </c>
-      <c r="O87" s="9">
+      <c r="O87" s="5">
         <v>0.4</v>
       </c>
     </row>
     <row r="88" spans="11:19">
-      <c r="K88" s="6"/>
-      <c r="L88" s="6"/>
-      <c r="M88" s="6"/>
-      <c r="N88" s="6"/>
-      <c r="O88" s="6"/>
+      <c r="K88" s="4"/>
+      <c r="L88" s="4"/>
+      <c r="M88" s="4"/>
+      <c r="N88" s="4"/>
+      <c r="O88" s="4"/>
       <c r="Q88">
         <f>SUM(N80:N87)</f>
         <v>76</v>
@@ -1499,54 +1500,60 @@
       </c>
     </row>
     <row r="89" spans="11:19">
-      <c r="K89" s="7" t="s">
+      <c r="K89" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="L89" s="8"/>
-      <c r="M89" s="16"/>
-      <c r="N89" s="16"/>
-      <c r="O89" s="9">
+      <c r="L89" s="15"/>
+      <c r="M89" s="8"/>
+      <c r="N89" s="8"/>
+      <c r="O89" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="11:19">
-      <c r="K90" s="6"/>
-      <c r="L90" s="6"/>
-      <c r="M90" s="6"/>
-      <c r="N90" s="6"/>
-      <c r="O90" s="6"/>
+      <c r="K90" s="4"/>
+      <c r="L90" s="4"/>
+      <c r="M90" s="4"/>
+      <c r="N90" s="4"/>
+      <c r="O90" s="4"/>
     </row>
     <row r="91" spans="11:19">
-      <c r="K91" s="12" t="s">
+      <c r="K91" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="L91" s="13"/>
-      <c r="M91" s="14"/>
-      <c r="N91" s="14"/>
-      <c r="O91" s="15">
+      <c r="L91" s="11"/>
+      <c r="M91" s="6"/>
+      <c r="N91" s="6"/>
+      <c r="O91" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="11:19">
-      <c r="K92" s="17"/>
-      <c r="L92" s="17"/>
-      <c r="M92" s="17"/>
-      <c r="N92" s="17"/>
-      <c r="O92" s="17"/>
+      <c r="K92" s="9"/>
+      <c r="L92" s="9"/>
+      <c r="M92" s="9"/>
+      <c r="N92" s="9"/>
+      <c r="O92" s="9"/>
     </row>
     <row r="93" spans="11:19">
-      <c r="K93" s="18" t="s">
+      <c r="K93" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="L93" s="18"/>
-      <c r="M93" s="18"/>
-      <c r="N93" s="19" t="s">
+      <c r="L93" s="12"/>
+      <c r="M93" s="12"/>
+      <c r="N93" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="O93" s="19"/>
+      <c r="O93" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="K74:L74"/>
+    <mergeCell ref="K66:O66"/>
+    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="K69:L69"/>
+    <mergeCell ref="K71:L71"/>
+    <mergeCell ref="K72:N72"/>
     <mergeCell ref="K91:L91"/>
     <mergeCell ref="K93:M93"/>
     <mergeCell ref="N93:O93"/>
@@ -1556,12 +1563,6 @@
     <mergeCell ref="K83:L83"/>
     <mergeCell ref="K86:L86"/>
     <mergeCell ref="K89:L89"/>
-    <mergeCell ref="K66:O66"/>
-    <mergeCell ref="K67:L67"/>
-    <mergeCell ref="K69:L69"/>
-    <mergeCell ref="K71:L71"/>
-    <mergeCell ref="K72:N72"/>
-    <mergeCell ref="K74:L74"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1570,102 +1571,159 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FFA43B4-F849-4C3C-B230-1745956A97B5}">
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="B1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:1">
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:1">
+      <c r="B3">
+        <v>55.712814000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:1">
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:1">
+      <c r="B5">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:1">
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:1">
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:1">
+      <c r="B8">
+        <v>54.600002000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:1">
+      <c r="B9">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="11" spans="1:1">
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="12" spans="1:1">
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="13" spans="1:1">
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" spans="1:1">
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="15" spans="1:1">
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="16" spans="1:1">
+      <c r="B15">
+        <v>23.200001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>36</v>
+      </c>
+      <c r="B19">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
